--- a/data/historico/semana_325.xlsx
+++ b/data/historico/semana_325.xlsx
@@ -31,7 +31,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$H$39</definedName>
   </definedNames>
@@ -4989,7 +4989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5001,7 +5001,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (5 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
+          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (8 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="B4" s="36" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="C4" s="36" t="inlineStr">
@@ -5075,73 +5075,139 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>Cicero Isrrael Sanabria</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="36" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="36" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D6" s="36" t="inlineStr">
+        <is>
+          <t>Gilmar Bitencourt Luiz</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="36" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="36" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D7" s="36" t="inlineStr">
+        <is>
+          <t>Rafael Ramos Recalde</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="37" t="inlineStr">
         <is>
           <t>22/09/2026</t>
         </is>
       </c>
-      <c r="B5" s="37" t="inlineStr">
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>22/09/2026</t>
         </is>
       </c>
-      <c r="C5" s="37" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
         <is>
           <t>Chuva (confirmada)</t>
         </is>
       </c>
-      <c r="D5" s="37" t="inlineStr">
+      <c r="D8" s="37" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="37" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>22/09/2026</t>
         </is>
       </c>
-      <c r="B6" s="37" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>22/09/2026</t>
         </is>
       </c>
-      <c r="C6" s="37" t="inlineStr">
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>Chuva (confirmada)</t>
         </is>
       </c>
-      <c r="D6" s="37" t="inlineStr">
+      <c r="D9" s="37" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="37" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t>22/09/2026</t>
         </is>
       </c>
-      <c r="B7" s="37" t="inlineStr">
+      <c r="B10" s="37" t="inlineStr">
         <is>
           <t>22/09/2026</t>
         </is>
       </c>
-      <c r="C7" s="37" t="inlineStr">
+      <c r="C10" s="37" t="inlineStr">
         <is>
           <t>Chuva (confirmada)</t>
         </is>
       </c>
-      <c r="D7" s="37" t="inlineStr">
+      <c r="D10" s="37" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D7"/>
+  <autoFilter ref="A2:D10"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
